--- a/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_transistor_small.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_transistor_small.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="padim" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stfpm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="uflow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,105 +478,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -589,116 +580,107 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>11.68335437774658</v>
+        <v>11.30003094673157</v>
       </c>
       <c r="D2" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0393103435635566</v>
+        <v>0.1452084332704544</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8470588326454163</v>
+        <v>0.7804877758026123</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7524752616882324</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8172042965888977</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.364875465631485</v>
+        <v>0.2856093347072601</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06977116316556931</v>
+        <v>0.0181455405553181</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0553592443466186</v>
+        <v>0.0549262285232543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0194024578730265</v>
+        <v>0.0435951471328735</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0791307139396667</v>
+        <v>5.443662166595459</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0649415222803751</v>
+        <v>16.47786855697632</v>
       </c>
       <c r="O2" t="n">
-        <v>5.820737361907959</v>
-      </c>
-      <c r="P2" t="n">
-        <v>23.73921418190002</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>19.48245668411255</v>
+        <v>13.07854413986206</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-164932</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-155025</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -710,116 +692,107 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>11.40979814529419</v>
+        <v>11.16498351097107</v>
       </c>
       <c r="D3" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0383649803698062</v>
+        <v>0.1306165754795074</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.7714285850524902</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8292682766914368</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3652730584144592</v>
+        <v>0.2848542928695678</v>
       </c>
       <c r="J3" t="n">
-        <v>0.069018617272377</v>
+        <v>0.0182067282994588</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0561236552894115</v>
+        <v>0.0555634888013203</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0189062666893005</v>
+        <v>0.0428547676404317</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07849724213282259</v>
+        <v>5.462018489837647</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0658121713002522</v>
+        <v>16.66904664039612</v>
       </c>
       <c r="O3" t="n">
-        <v>5.671880006790161</v>
-      </c>
-      <c r="P3" t="n">
-        <v>23.5491726398468</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>19.74365139007568</v>
+        <v>12.85643029212952</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-165111</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-155204</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -831,116 +804,107 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>11.50611615180969</v>
+        <v>11.38571643829346</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9300000071525574</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0388971231877803</v>
+        <v>0.1282634437084198</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8536585569381714</v>
+        <v>0.8354430198669434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8444444537162781</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7567567825317383</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3667322695255279</v>
+        <v>0.2907535433769226</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0693816021084785</v>
+        <v>0.0182543118794759</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0565278679132461</v>
+        <v>0.0555905389785766</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0189049975077311</v>
+        <v>0.0418489241600036</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0790448506673177</v>
+        <v>5.476293563842773</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0661170975367228</v>
+        <v>16.677161693573</v>
       </c>
       <c r="O4" t="n">
-        <v>5.671499252319336</v>
-      </c>
-      <c r="P4" t="n">
-        <v>23.71345520019531</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>19.83512926101685</v>
+        <v>12.5546772480011</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-165310</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-155343</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -952,116 +916,107 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>11.43281555175781</v>
+        <v>11.51615023612976</v>
       </c>
       <c r="D5" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0383386611938476</v>
+        <v>0.1439627110958099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7777777910232544</v>
+        <v>0.8219178318977356</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7341772317886353</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3661243617534637</v>
+        <v>0.2850193381309509</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0696283802390098</v>
+        <v>0.0181667677561442</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0560986623167991</v>
+        <v>0.0554126135508219</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0187856419881184</v>
+        <v>0.0430612063407898</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0787837862968444</v>
+        <v>5.450030326843262</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06507453997929891</v>
+        <v>16.62378406524658</v>
       </c>
       <c r="O5" t="n">
-        <v>5.635692596435547</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.63513588905334</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>19.52236199378968</v>
+        <v>12.91836190223694</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-165510</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-155522</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1073,116 +1028,107 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>11.65881943702698</v>
+        <v>11.04698443412781</v>
       </c>
       <c r="D6" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E6" t="n">
-        <v>0.038479920476675</v>
+        <v>0.1470703929662704</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7872340679168701</v>
+        <v>0.8048780560493469</v>
       </c>
       <c r="G6" t="n">
-        <v>0.747474730014801</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.367493063211441</v>
+        <v>0.2899933755397796</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0692397430539131</v>
+        <v>0.0180619597434997</v>
       </c>
       <c r="K6" t="n">
-        <v>0.056007232517004</v>
+        <v>0.0545693858464558</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0193205261230468</v>
+        <v>0.0415684628486633</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07852327903111769</v>
+        <v>5.418587923049927</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06552839358647659</v>
+        <v>16.37081575393677</v>
       </c>
       <c r="O6" t="n">
-        <v>5.796157836914063</v>
-      </c>
-      <c r="P6" t="n">
-        <v>23.55698370933533</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>19.658518075943</v>
+        <v>12.470538854599</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-165649</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-155701</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,105 +1194,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -1357,119 +1293,110 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>30.82412695884705</v>
+        <v>360.3540661334992</v>
       </c>
       <c r="D2" t="n">
-        <v>1.759999990463257</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0546837463974952</v>
+        <v>0.1297866362027632</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5611510872840881</v>
+        <v>0.7749999761581421</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5714285969734192</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1825669705867767</v>
+        <v>0.2837131917476654</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0612420924007892</v>
+        <v>0.0183846910794576</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0519031733274459</v>
+        <v>0.0455498806635538</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0137534872690836</v>
+        <v>0.0355197874704996</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07257228453954059</v>
+        <v>5.51540732383728</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0636966800689697</v>
+        <v>13.66496419906616</v>
       </c>
       <c r="O2" t="n">
-        <v>4.126046180725098</v>
-      </c>
-      <c r="P2" t="n">
-        <v>21.77168536186218</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>19.10900402069092</v>
+        <v>10.6559362411499</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250716-005153</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-171215</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1478,119 +1405,110 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>30.92816925048828</v>
+        <v>253.7193903923035</v>
       </c>
       <c r="D3" t="n">
-        <v>1.759999990463257</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0537809140980243</v>
+        <v>0.1304039328738495</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5611510872840881</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5714285969734192</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1816203594207763</v>
+        <v>0.2862828969955444</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0598220825195312</v>
+        <v>0.0171896934509277</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0518363416194915</v>
+        <v>0.0454799350102742</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0133597834904988</v>
+        <v>0.035655022462209</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0711186075210571</v>
+        <v>5.15690803527832</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0638049872716267</v>
+        <v>13.64398050308228</v>
       </c>
       <c r="O3" t="n">
-        <v>4.007935047149658</v>
-      </c>
-      <c r="P3" t="n">
-        <v>21.33558225631714</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>19.14149618148804</v>
+        <v>10.69650673866272</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250716-005935</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-171410</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1599,119 +1517,110 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>31.10761547088623</v>
+        <v>266.3881750106812</v>
       </c>
       <c r="D4" t="n">
-        <v>1.740000009536743</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0497433014214038</v>
+        <v>0.1292530644152845</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5862069129943848</v>
+        <v>0.782608687877655</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5588235259056091</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5714285969734192</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.353654533624649</v>
+        <v>0.2806296944618225</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0613983608782291</v>
+        <v>0.0173777016003926</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0521009750664234</v>
+        <v>0.0456072719891866</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01910946448644</v>
+        <v>0.0358252986272176</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0725758775075276</v>
+        <v>5.213310480117798</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0634422596295674</v>
+        <v>13.68218159675598</v>
       </c>
       <c r="O4" t="n">
-        <v>5.732839345932007</v>
-      </c>
-      <c r="P4" t="n">
-        <v>21.7727632522583</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>19.03267788887024</v>
+        <v>10.74758958816528</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250716-010531</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-171603</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1720,119 +1629,110 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>30.87985229492188</v>
+        <v>314.6764166355133</v>
       </c>
       <c r="D5" t="n">
-        <v>1.730000019073486</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0535538531839847</v>
+        <v>0.1307192201561787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.569343090057373</v>
+        <v>0.7764706015586853</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5714285969734192</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5714285969734192</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.186187207698822</v>
+        <v>0.2904409170150757</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0614764802157878</v>
+        <v>0.0171615735689799</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0516447238624095</v>
+        <v>0.0456422917048136</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0135330311457316</v>
+        <v>0.0357024526596069</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0725085711479187</v>
+        <v>5.14847207069397</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0630954384803772</v>
+        <v>13.69268751144409</v>
       </c>
       <c r="O5" t="n">
-        <v>4.059909343719482</v>
-      </c>
-      <c r="P5" t="n">
-        <v>21.75257134437561</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>18.92863154411316</v>
+        <v>10.71073579788208</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250716-011139</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-171759</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>small</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1841,119 +1741,826 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>30.79808449745178</v>
+        <v>223.818029165268</v>
       </c>
       <c r="D6" t="n">
-        <v>1.730000019073486</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0564089894294738</v>
+        <v>0.1295519645015398</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5611510872840881</v>
+        <v>0.7272727489471436</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5507246255874634</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1803593933582306</v>
+        <v>0.2868738174438476</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0604881569743156</v>
+        <v>0.0172292343775431</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0514190569519996</v>
+        <v>0.045183842976888</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0131784335772196</v>
+        <v>0.0363733061154683</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0715532422065734</v>
+        <v>5.16877031326294</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0633000826835632</v>
+        <v>13.55515289306641</v>
       </c>
       <c r="O6" t="n">
-        <v>3.953530073165894</v>
-      </c>
-      <c r="P6" t="n">
-        <v>21.46597266197205</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>18.99002480506897</v>
+        <v>10.9119918346405</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250716-011834</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-171952</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>mvtec_transistor_small</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>training:epoch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>training:e2e_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>training:gpu_mem</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>training:train/iter_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>data_group</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>otx_version</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>otx_ref</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>test_branch</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>test_commit</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_info</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>accelerator_info</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>machine_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1065.940366744995</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.289999961853027</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1566668070440915</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6881720423698425</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6384649872779846</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0306639838218688</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.07939661184946691</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.07288225412368771</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.199195146560667</v>
+      </c>
+      <c r="N2" t="n">
+        <v>23.81898355484009</v>
+      </c>
+      <c r="O2" t="n">
+        <v>21.86467623710632</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250715-022149</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>mvtec_transistor_small</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>199</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1075.662474393845</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.380000114440918</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1562334302831534</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6744186282157898</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5102844834327698</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0268109981218973</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.07855668703715001</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.07168533484141031</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8.043299436569214</v>
+      </c>
+      <c r="N3" t="n">
+        <v>23.56700611114502</v>
+      </c>
+      <c r="O3" t="n">
+        <v>21.5056004524231</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250715-024126</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>mvtec_transistor_small</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>199</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1068.41163110733</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1574474701180529</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7228915691375732</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5808688998222351</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0287030132611592</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.07617122173309319</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.072578850587209</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8.610903978347778</v>
+      </c>
+      <c r="N4" t="n">
+        <v>22.85136651992798</v>
+      </c>
+      <c r="O4" t="n">
+        <v>21.77365517616272</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250715-030110</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>mvtec_transistor_small</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>199</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1070.644601821899</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.369999885559082</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1580352248558446</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7400000095367432</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5417347550392151</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0282731127738952</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0773960598309834</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0703371397654215</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8.481933832168579</v>
+      </c>
+      <c r="N5" t="n">
+        <v>23.21881794929504</v>
+      </c>
+      <c r="O5" t="n">
+        <v>21.10114192962646</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250715-032109</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>mvtec_transistor_small</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>199</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1062.706089019775</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.369999885559082</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1620674634249365</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6666666865348816</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.541783332824707</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0274445915222168</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0785422428448995</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.073096657594045</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8.233377456665039</v>
+      </c>
+      <c r="N6" t="n">
+        <v>23.56267285346985</v>
+      </c>
+      <c r="O6" t="n">
+        <v>21.9289972782135</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250715-034109</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_transistor_small</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_transistor_small</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
